--- a/docs/Decodifiche/168_dmnm_dec_stato_civile.xlsx
+++ b/docs/Decodifiche/168_dmnm_dec_stato_civile.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Celibe/Nubile</t>
   </si>
   <si>
-    <t>2025-12-02 20:24:14.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -59,9 +59,6 @@
     <t>Divorziato/a</t>
   </si>
   <si>
-    <t>2025-12-02 20:24:15.0</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
   </si>
   <si>
     <t>Non classificabile/ignoto/n.c</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:24:16.0</t>
   </si>
 </sst>
 </file>
@@ -237,7 +231,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -248,87 +242,87 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
